--- a/Principal wellbeing email triage tool.xlsx
+++ b/Principal wellbeing email triage tool.xlsx
@@ -252,7 +252,7 @@
     <t xml:space="preserve">Pick a greeting and add a name, e.g. 'Good morning Damien,'</t>
   </si>
   <si>
-    <t xml:space="preserve">Select Yes, No or Maybe in the question slicers below - you do not need to answer every question; unanswered ones are simply left out of the draft. For recurring queries, pick a common response override instead. Then add a greeting, name and topic under 'Draft email reply' and copy the finished draft into Outlook.</t>
+    <t xml:space="preserve">Select Yes, No or Maybe in the question slicers below - you do not need to answer every question; unanswered ones are simply left out of the draft. For recurring queries, pick a common response override instead. Then add a greeting, name and topic under 'Draft email reply' and copy the finished draft into Outlook. To clear a slicer, click the funnel-with-x button in its top right corner.</t>
   </si>
   <si>
     <t xml:space="preserve">Edit the modular wording on the Response library tab and the recurring full responses on the Preset responses tab. The draft remains a starting point: add case-specific detail and confirm the final advice against current Ikon guidance before sending.</t>
@@ -2848,7 +2848,6 @@
       </c>
       <c r="B2">
         <f>SUBTOTAL(103,A2)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2857,7 +2856,6 @@
       </c>
       <c r="B3">
         <f>SUBTOTAL(103,A3)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2866,7 +2864,6 @@
       </c>
       <c r="B4">
         <f>SUBTOTAL(103,A4)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2883,7 +2880,6 @@
       </c>
       <c r="B7">
         <f>SUBTOTAL(103,A7)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2892,7 +2888,6 @@
       </c>
       <c r="B8">
         <f>SUBTOTAL(103,A8)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2901,7 +2896,6 @@
       </c>
       <c r="B9">
         <f>SUBTOTAL(103,A9)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2918,7 +2912,6 @@
       </c>
       <c r="B12">
         <f>SUBTOTAL(103,A12)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2927,7 +2920,6 @@
       </c>
       <c r="B13">
         <f>SUBTOTAL(103,A13)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2936,7 +2928,6 @@
       </c>
       <c r="B14">
         <f>SUBTOTAL(103,A14)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2953,7 +2944,6 @@
       </c>
       <c r="B17">
         <f>SUBTOTAL(103,A17)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2962,7 +2952,6 @@
       </c>
       <c r="B18">
         <f>SUBTOTAL(103,A18)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2971,7 +2960,6 @@
       </c>
       <c r="B19">
         <f>SUBTOTAL(103,A19)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2988,7 +2976,6 @@
       </c>
       <c r="B22">
         <f>SUBTOTAL(103,A22)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2997,7 +2984,6 @@
       </c>
       <c r="B23">
         <f>SUBTOTAL(103,A23)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3006,7 +2992,6 @@
       </c>
       <c r="B24">
         <f>SUBTOTAL(103,A24)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3023,7 +3008,6 @@
       </c>
       <c r="B27">
         <f>SUBTOTAL(103,A27)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3032,7 +3016,6 @@
       </c>
       <c r="B28">
         <f>SUBTOTAL(103,A28)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3041,7 +3024,6 @@
       </c>
       <c r="B29">
         <f>SUBTOTAL(103,A29)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3058,7 +3040,6 @@
       </c>
       <c r="B32">
         <f>SUBTOTAL(103,A32)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3067,7 +3048,6 @@
       </c>
       <c r="B33">
         <f>SUBTOTAL(103,A33)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3076,7 +3056,6 @@
       </c>
       <c r="B34">
         <f>SUBTOTAL(103,A34)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3093,7 +3072,6 @@
       </c>
       <c r="B37">
         <f>SUBTOTAL(103,A37)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3102,7 +3080,6 @@
       </c>
       <c r="B38">
         <f>SUBTOTAL(103,A38)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3164,63 +3141,48 @@
     <row r="40" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J40" t="str">
         <f>IF(SUM($B$2:$B$4)=1,INDEX($A$2:$A$4,MATCH(1,$B$2:$B$4,0)),"")</f>
-        <v/>
       </c>
       <c r="K40" t="str">
         <f>IF(SUM($B$7:$B$9)=1,INDEX($A$7:$A$9,MATCH(1,$B$7:$B$9,0)),"")</f>
-        <v/>
       </c>
       <c r="L40" t="str">
         <f>IF(SUM($B$12:$B$14)=1,INDEX($A$12:$A$14,MATCH(1,$B$12:$B$14,0)),"")</f>
-        <v/>
       </c>
       <c r="M40" t="str">
         <f>IF(SUM($B$17:$B$19)=1,INDEX($A$17:$A$19,MATCH(1,$B$17:$B$19,0)),"")</f>
-        <v/>
       </c>
       <c r="N40" t="str">
         <f>IF(SUM($B$22:$B$24)=1,INDEX($A$22:$A$24,MATCH(1,$B$22:$B$24,0)),"")</f>
-        <v/>
       </c>
       <c r="O40" t="str">
         <f>IF(SUM($B$27:$B$29)=1,INDEX($A$27:$A$29,MATCH(1,$B$27:$B$29,0)),"")</f>
-        <v/>
       </c>
       <c r="P40" t="str">
         <f>IF(SUM($B$32:$B$34)=1,INDEX($A$32:$A$34,MATCH(1,$B$32:$B$34,0)),"")</f>
-        <v/>
       </c>
       <c r="Q40" t="str">
         <f>IF(SUM($B$37:$B$38)=1,INDEX($A$37:$A$38,MATCH(1,$B$37:$B$38,0)),"")</f>
-        <v/>
       </c>
       <c r="R40" t="str">
         <f>IF($J$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Q1|"&amp;$J$40,'Response library'!$E$2:$E$24,0)),""))</f>
-        <v/>
       </c>
       <c r="S40" t="str">
         <f>IF($K$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Q2|"&amp;$K$40,'Response library'!$E$2:$E$24,0)),""))</f>
-        <v/>
       </c>
       <c r="T40" t="str">
         <f>IF($L$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Q3|"&amp;$L$40,'Response library'!$E$2:$E$24,0)),""))</f>
-        <v/>
       </c>
       <c r="U40" t="str">
         <f>IF($M$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Q4|"&amp;$M$40,'Response library'!$E$2:$E$24,0)),""))</f>
-        <v/>
       </c>
       <c r="V40" t="str">
         <f>IF($N$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Q5|"&amp;$N$40,'Response library'!$E$2:$E$24,0)),""))</f>
-        <v/>
       </c>
       <c r="W40" t="str">
         <f>IF($O$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Q6|"&amp;$O$40,'Response library'!$E$2:$E$24,0)),""))</f>
-        <v/>
       </c>
       <c r="X40" t="str">
         <f>IF($P$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Panel|"&amp;$P$40,'Response library'!$E$2:$E$24,0)),""))</f>
-        <v/>
       </c>
       <c r="Y40" t="str">
         <f>IF($Q$40="","",IFERROR(T(INDEX('Response library'!$D$2:$D$24,MATCH("Travel|"&amp;$Q$40,'Response library'!$E$2:$E$24,0))),""))</f>
@@ -3943,8 +3905,10 @@
       <c r="A5" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>131</v>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Draft email body</t>
+        </is>
       </c>
       <c r="C5" s="4" t="s">
         <v>64</v>

--- a/Principal wellbeing email triage tool.xlsx
+++ b/Principal wellbeing email triage tool.xlsx
@@ -105,7 +105,7 @@
     <t>Does this align with the panel of wellbeing service providers?</t>
   </si>
   <si>
-    <t>Does this involve travel or accommodation?</t>
+    <t xml:space="preserve">Does this involve travel or accommodation?</t>
   </si>
   <si>
     <t xml:space="preserve">Tip: to clear a slicer, select the small red 'X' funnel button in its top right corner.</t>
@@ -1784,8 +1784,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="TravelSlicerSource" displayName="TravelSlicerSource" ref="A36:B38" totalsRowShown="0">
-  <autoFilter ref="A36:B38" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="TravelSlicerSource" displayName="TravelSlicerSource" ref="A36:B39" totalsRowShown="0">
+  <autoFilter ref="A36:B39" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Travel"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Visible row"/>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="35" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="str">
-        <f>TRIM(IF($D$33="","Hi",$D$33)&amp;" "&amp;TRIM($E$33))&amp;","&amp;CHAR(10)&amp;CHAR(10)&amp;IF(TRIM($D$34)="","Thank you for reaching out regarding the principal wellbeing targeted funding.","Thank you for reaching out regarding "&amp;TRIM($D$34)&amp;".")&amp;CHAR(10)&amp;CHAR(10)&amp;IF('Preset responses'!$F$2&lt;&gt;"",'Preset responses'!$F$2,IF(COUNTIF('Pivot source data'!$J$40:$Q$40,"?*")=0,"[Select an answer in one or more question slicers above, or pick a common response override, to build the body of the email.]",'Pivot source data'!$AA$40))&amp;CHAR(10)&amp;CHAR(10)&amp;"If you have any further questions, please reach out again. You can contact Principal wellbeing expenditure support by phone on 9264 4201 or by email at whsw.staffwellbeing@education.wa.edu.au."&amp;CHAR(10)&amp;CHAR(10)&amp;"Kind regards,"</f>
+        <f>TRIM(IF($D$33="","Hi",$D$33)&amp;" "&amp;TRIM($E$33))&amp;","&amp;CHAR(10)&amp;CHAR(10)&amp;IF(TRIM($D$34)="","Thank you for reaching out regarding the principal wellbeing targeted funding.","Thank you for reaching out regarding "&amp;TRIM($D$34)&amp;".")&amp;CHAR(10)&amp;CHAR(10)&amp;IF('Preset responses'!$F$2&lt;&gt;"",'Preset responses'!$F$2,IF(COUNTIF('Pivot source data'!$J$40:$Q$40,"?*")=0,"[Select an answer in one or more question slicers above, or pick a common response override, to build the body of the email.]",IF('Pivot source data'!$AA$40="","[The answers selected so far do not add any wording to the email - answer more of the question slicers above.]",'Pivot source data'!$AA$40)))&amp;CHAR(10)&amp;CHAR(10)&amp;"If you have any further questions, please reach out again. You can contact Principal wellbeing expenditure support by phone on 9264 4201 or by email at whsw.staffwellbeing@education.wa.edu.au."&amp;CHAR(10)&amp;CHAR(10)&amp;"Kind regards,"</f>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
@@ -3083,6 +3083,12 @@
       </c>
     </row>
     <row r="39" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39">
+        <f>SUBTOTAL(103,A39)</f>
+      </c>
       <c r="J39" t="s">
         <v>75</v>
       </c>
@@ -3161,7 +3167,7 @@
         <f>IF(SUM($B$32:$B$34)=1,INDEX($A$32:$A$34,MATCH(1,$B$32:$B$34,0)),"")</f>
       </c>
       <c r="Q40" t="str">
-        <f>IF(SUM($B$37:$B$38)=1,INDEX($A$37:$A$38,MATCH(1,$B$37:$B$38,0)),"")</f>
+        <f>IF(SUM($B$37:$B$39)=1,INDEX($A$37:$A$39,MATCH(1,$B$37:$B$39,0)),"")</f>
       </c>
       <c r="R40" t="str">
         <f>IF($J$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Q1|"&amp;$J$40,'Response library'!$E$2:$E$24,0)),""))</f>
@@ -3185,7 +3191,7 @@
         <f>IF($P$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Panel|"&amp;$P$40,'Response library'!$E$2:$E$24,0)),""))</f>
       </c>
       <c r="Y40" t="str">
-        <f>IF($Q$40="","",IFERROR(T(INDEX('Response library'!$D$2:$D$24,MATCH("Travel|"&amp;$Q$40,'Response library'!$E$2:$E$24,0))),""))</f>
+        <f>IF($Q$40="","",IFERROR(T(INDEX('Response library'!$D$2:$D$25,MATCH("Travel|"&amp;$Q$40,'Response library'!$E$2:$E$25,0))),""))</f>
       </c>
       <c r="Z40" t="str">
         <f>IF(COUNTIF($J$40:$O$40,"?*")=0,"",IF(COUNTIF($J$40:$O$40,"No")&gt;0,"To answer briefly: based on the decision-making framework, this expenditure does not appear to be appropriate. Please see the detail below.",IF(COUNTIF($J$40:$O$40,"Yes")=6,"To answer briefly: based on the decision-making framework, this expenditure is likely to be appropriate. Please see the detail below.","To answer briefly: we need a little more information before this expenditure can be confirmed as appropriate. Please see the detail below.")))</f>
@@ -3406,7 +3412,7 @@
   <sheetPr>
     <tabColor rgb="FFE5803A"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3847,8 +3853,27 @@
         <v>Travel|No</v>
       </c>
     </row>
+    <row r="25" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is not yet clear whether travel or accommodation will be involved. If it is, it may be funded where it supports the eligible wellbeing activity, in line with the Official Travel Policy - please check the approval requirements with us before booking.</t>
+        </is>
+      </c>
+      <c r="E25" s="5">
+        <f>A25&amp;"|"&amp;C25</f>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E24" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:E25" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>

--- a/Principal wellbeing email triage tool.xlsx
+++ b/Principal wellbeing email triage tool.xlsx
@@ -444,7 +444,7 @@
     <t xml:space="preserve">As the query involves travel or accommodation: the funding may be used for travel and accommodation where it is required to support access to an eligible principal wellbeing activity, in line with the Official Travel Policy and the associated Official Air Travel and Travel Accommodation, Meal and Other Expenses procedures. Travellers cannot approve their own travel - please seek approval from an Assistant Director of Education or above prior to booking. The funding is not intended to be used solely for travel or accommodation.</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">As the query does not involve travel or accommodation, no travel approvals apply.</t>
   </si>
   <si>
     <t>Common response overrides</t>

--- a/Principal wellbeing email triage tool.xlsx
+++ b/Principal wellbeing email triage tool.xlsx
@@ -3191,7 +3191,7 @@
         <f>IF($P$40="","",IFERROR(INDEX('Response library'!$D$2:$D$24,MATCH("Panel|"&amp;$P$40,'Response library'!$E$2:$E$24,0)),""))</f>
       </c>
       <c r="Y40" t="str">
-        <f>IF($Q$40="","",IFERROR(T(INDEX('Response library'!$D$2:$D$25,MATCH("Travel|"&amp;$Q$40,'Response library'!$E$2:$E$25,0))),""))</f>
+        <f>IF($Q$40="","",IFERROR(INDEX('Response library'!$D$2:$D$25,MATCH("Travel|"&amp;$Q$40,'Response library'!$E$2:$E$25,0)),""))</f>
       </c>
       <c r="Z40" t="str">
         <f>IF(COUNTIF($J$40:$O$40,"?*")=0,"",IF(COUNTIF($J$40:$O$40,"No")&gt;0,"To answer briefly: based on the decision-making framework, this expenditure does not appear to be appropriate. Please see the detail below.",IF(COUNTIF($J$40:$O$40,"Yes")=6,"To answer briefly: based on the decision-making framework, this expenditure is likely to be appropriate. Please see the detail below.","To answer briefly: we need a little more information before this expenditure can be confirmed as appropriate. Please see the detail below.")))</f>
